--- a/results/result_evaluation_logs/I_Advance_Adaption_One_Agent.xlsx
+++ b/results/result_evaluation_logs/I_Advance_Adaption_One_Agent.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,6 @@
           <t>Result String</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -626,11 +621,6 @@
 </t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0db09a2a-3c0f-4a0d-80d1-2dabdc278aac</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -705,11 +695,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q20992419 wd:P136 wd:Q17516 .
 </t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>6b76d8e2-13df-4150-baf9-99a724b1fae9</t>
         </is>
       </c>
     </row>
@@ -790,11 +775,6 @@
 </t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>655bd24e-e0fb-4eb4-9a46-1651f4c68338</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -840,10 +820,10 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
@@ -874,11 +854,6 @@
 </t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5d37ab9e-bedd-4789-a7e6-18e06a917f33</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -953,11 +928,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q36771 wd:P27 wd:Q29999 .
 </t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>a8129173-89db-4db6-a1e9-c7b1829d84bc</t>
         </is>
       </c>
     </row>
@@ -1036,11 +1006,6 @@
 </t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>86d7f5a0-2969-4dd7-be5f-2bb359f74c01</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1116,11 +1081,6 @@
 wd:Q2226643 wd:P31 wd:Q65943 .
 wd:Q2226643 wd:P138 wd:Q28937 .
 </t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>755fa257-0e34-4e70-b51a-656216724bf6</t>
         </is>
       </c>
     </row>
@@ -1203,11 +1163,6 @@
 </t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>05c0d5bf-d796-49fb-8658-515c4b220e81</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1288,11 +1243,6 @@
 </t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>f429574e-a66d-4069-b5a4-cb8fa6e1b981</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1371,11 +1321,6 @@
 </t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>beb66e72-0f53-4540-85b2-c0d8aa50ba1c</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1451,11 +1396,6 @@
 </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8b247246-50f2-4525-950a-44bcc9236eb2</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1531,11 +1471,6 @@
 wd:Q516760 wd:P276 wd:Q1605654 .
 wd:Q516760 wd:P710 wd:Q271108 .
 </t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2201c9ad-bb5d-477e-a89f-e1a2efbb0115</t>
         </is>
       </c>
     </row>
@@ -1617,11 +1552,6 @@
 </t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>f5344efa-9e9d-4337-9242-a7320e77a085</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1700,11 +1630,6 @@
 </t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>e82c3451-73de-4a97-9110-5bdd8f2698f5</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1781,11 +1706,6 @@
 </t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>0c383d14-fcfb-4e14-82cd-35077d42c3af</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1863,11 +1783,6 @@
 </t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>fec24624-1211-48b8-963d-4b22208736fa</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1946,11 +1861,6 @@
 </t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>379be976-84c0-4d34-9a52-de0b3718a948</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2028,11 +1938,6 @@
 </t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>c97fe26c-5da4-4106-a05d-621f7a57d66e</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2107,11 +2012,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q20671544 wd:P412 wd:Q131454 .
 </t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>83f5d464-05ba-4bc9-b67f-6d60519a00f2</t>
         </is>
       </c>
     </row>
@@ -2193,11 +2093,6 @@
 </t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>fa386efb-f407-45e2-a535-43bd1ff0b6a6</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2274,11 +2169,6 @@
 </t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>0b7425b3-14e4-4fdf-8daf-c9db1e80fb42</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2355,11 +2245,6 @@
 </t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>0aa89c61-f8bc-4e72-89b3-2849262b63c8</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2437,11 +2322,6 @@
 </t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>5cdf1dcb-2a8d-4a14-b02a-50acea574766</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2517,11 +2397,6 @@
 </t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>bd671306-bfbf-4262-8010-5fe430559c95</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2599,11 +2474,6 @@
 </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>70008e58-2612-47ce-bbae-c1a79a6e1c44</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2681,11 +2551,6 @@
 </t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>63223f89-013c-405b-8911-645440883f4f</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2763,11 +2628,6 @@
 </t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>f6980c3e-0f37-4b2e-b005-1c7d81364124</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2846,11 +2706,6 @@
 </t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>4ff2ac22-5f13-4677-a818-d95d1cd27329</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2890,16 +2745,16 @@
         <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
         <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
         <v>2</v>
@@ -2926,11 +2781,6 @@
 wd:Q8083051 wd:P131 wd:Q1840968 .
 wd:Q8083051 wd:P17 wd:Q36 .
 </t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>e67c2262-73bd-4df2-be80-81bdb20b3c0d</t>
         </is>
       </c>
     </row>
@@ -3010,11 +2860,6 @@
 </t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>fe13bffb-c5d3-4b6d-ae9a-b6457b3bbf7d</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3091,11 +2936,6 @@
 </t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>b2083a78-7abe-46f7-8650-21e2ddc60678</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3141,10 +2981,10 @@
         <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>4</v>
@@ -3175,11 +3015,6 @@
 </t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>1fad71b0-76a7-4b75-ab43-b5486c8463b5</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3257,11 +3092,6 @@
 </t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>08f39099-45a5-4580-a38b-7e2928b7b4fd</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3338,11 +3168,6 @@
 </t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>de532bdf-fe89-4a80-9902-28cf455ef78f</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3419,11 +3244,6 @@
 </t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>e9c9d7f7-5ca0-41dc-a6e7-ee063ea47460</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3500,11 +3320,6 @@
 </t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>b5f33ed9-8903-47db-928d-1a3e4aa187f0</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3550,10 +3365,10 @@
         <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
         <v>2</v>
@@ -3580,11 +3395,6 @@
 wd:Q6803534 wd:P361 wd:Q1247390 .
 wd:Q6803534 wd:P17 wd:Q145 .
 </t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>e0521643-e267-4120-ab5a-cda7e4ebe091</t>
         </is>
       </c>
     </row>
@@ -3664,11 +3474,6 @@
 </t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>b4b95dce-a49d-401e-bd28-ff7e132a8586</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3745,11 +3550,6 @@
 </t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>50e682b1-84c6-4c6b-bb95-df9d8fa9184a</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3827,11 +3627,6 @@
 </t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>02f49ca8-8b7d-4de5-894f-c59ae860268d</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3871,7 +3666,7 @@
         <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
         <v>4</v>
@@ -3911,11 +3706,6 @@
 </t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>3ed8a869-0af3-403d-86ad-ad0cca5e47d7</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3992,11 +3782,6 @@
 </t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>c19a89d9-60c6-4203-b00e-789d4802050c</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4071,11 +3856,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q29644512 wd:P31 wd:Q1358919 .
 </t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>77180d3c-4ed8-4bef-832d-6a8e662ce368</t>
         </is>
       </c>
     </row>
@@ -4160,11 +3940,6 @@
 </t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>1f44c4da-5bbc-4d3d-9c5e-1d4921844c10</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4243,11 +4018,6 @@
 </t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>88c3863e-66c2-463d-b388-5a37f25a34cc</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4325,11 +4095,6 @@
 </t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>74a474c2-d699-40cd-8691-b97bac812db7</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4408,11 +4173,6 @@
 </t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>9d82339d-b5cc-45bd-900b-80461d6cd780</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4428,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -4437,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -4446,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4467,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4476,7 +4236,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -4485,11 +4245,6 @@
         <is>
           <t>Recursion limit of 20 reached without hitting a stop condition. You can increase the limit by setting the `recursion_limit` config key.
 For troubleshooting, visit: https://python.langchain.com/docs/troubleshooting/errors/GRAPH_RECURSION_LIMIT</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>3ff7ef02-87d0-4ccc-a8ba-aa3156b97a12</t>
         </is>
       </c>
     </row>
@@ -4537,10 +4292,10 @@
         <v>2</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
         <v>3</v>
@@ -4570,11 +4325,6 @@
 </t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>94ff3a2c-86e8-40bd-ae4e-28ea309ba547</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4649,11 +4399,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q2362697 wd:P556 wd:Q503601 .
 </t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>69e54b59-8a92-487f-a16f-360497fd354b</t>
         </is>
       </c>
     </row>
